--- a/code/output/model_performance.xlsx
+++ b/code/output/model_performance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,26 +466,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9642982149107455</v>
+        <v>0.9686328105468425</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9642057697100578</v>
+        <v>0.9685293221817567</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9642982149107455</v>
+        <v>0.9686328105468425</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9768902907221636</v>
+        <v>0.9798280278222845</v>
       </c>
       <c r="G2" t="n">
-        <v>0.964023713019734</v>
+        <v>0.968427932918792</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9907678308321465</v>
+        <v>0.9928389881302613</v>
       </c>
     </row>
     <row r="3">
@@ -496,56 +496,56 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>validation</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9699530046995301</v>
+        <v>0.9642982149107455</v>
       </c>
       <c r="D3" t="n">
-        <v>0.969864496493862</v>
+        <v>0.9642057697100578</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9699530046995301</v>
+        <v>0.9642982149107455</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9805563546239338</v>
+        <v>0.9768902907221636</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9697464795300955</v>
+        <v>0.964023713019734</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9924789254821275</v>
+        <v>0.9907678308321465</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Decision Tree</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>test</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9210960548027401</v>
+        <v>0.9699530046995301</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9209601993065444</v>
+        <v>0.969864496493862</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9210960548027401</v>
+        <v>0.9699530046995301</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9503503886603584</v>
+        <v>0.9805563546239338</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9210057055929792</v>
+        <v>0.9697464795300955</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9255255829905378</v>
+        <v>0.9924789254821275</v>
       </c>
     </row>
     <row r="5">
@@ -556,32 +556,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>train</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9215578442155784</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9215707056614443</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9215578442155784</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.950929980133783</v>
+        <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9215434069502429</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9263949702006744</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K-NN</t>
+          <t>Decision Tree</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9224461223061153</v>
+        <v>0.9210960548027401</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9236741757414144</v>
+        <v>0.9209601993065444</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9224461223061153</v>
+        <v>0.9210960548027401</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9473719405092819</v>
+        <v>0.9503503886603584</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9218125115615665</v>
+        <v>0.9210057055929792</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9619007051067705</v>
+        <v>0.9255255829905378</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K-NN</t>
+          <t>Decision Tree</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -620,81 +620,201 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9277572242775722</v>
+        <v>0.9215578442155784</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9289323960925385</v>
+        <v>0.9215707056614443</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9277572242775722</v>
+        <v>0.9215578442155784</v>
       </c>
       <c r="F7" t="n">
-        <v>0.950797950169247</v>
+        <v>0.950929980133783</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9272344324563389</v>
+        <v>0.9215434069502429</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9661538195465608</v>
+        <v>0.9263949702006744</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>K-NN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>validation</t>
+          <t>train</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9488474423721186</v>
+        <v>0.937282288038134</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9487195954844315</v>
+        <v>0.9382426734615221</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9488474423721186</v>
+        <v>0.937282288038134</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9655833291570998</v>
+        <v>0.9573418549568928</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9480658948683208</v>
+        <v>0.9367091114849593</v>
       </c>
       <c r="H8" t="n">
-        <v>0.979140769120023</v>
+        <v>0.9893474404393636</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>K-NN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9224461223061153</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9236741757414144</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.9224461223061153</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9473719405092819</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9218125115615665</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9619007051067705</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>K-NN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9277572242775722</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.9289323960925385</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9277572242775722</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.950797950169247</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9272344324563389</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9661538195465608</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>SVM</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>train</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9525158752645877</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9523531950337825</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.9525158752645877</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.967949318787508</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9518445399400774</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9820233042175897</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.9488474423721186</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.9487195954844315</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9488474423721186</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9655833291570998</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9480658948683208</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.979140769120023</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>test</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C13" t="n">
         <v>0.9547045295470453</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D13" t="n">
         <v>0.954654060168205</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E13" t="n">
         <v>0.9547045295470453</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F13" t="n">
         <v>0.9693121484525511</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G13" t="n">
         <v>0.9541081708018527</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H13" t="n">
         <v>0.9820562537105441</v>
       </c>
     </row>

--- a/code/output/model_performance.xlsx
+++ b/code/output/model_performance.xlsx
@@ -1,34 +1,82 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="performance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="performance" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="15">
+  <si>
+    <t>model</t>
+  </si>
+  <si>
+    <t>split</t>
+  </si>
+  <si>
+    <t>accuracy</t>
+  </si>
+  <si>
+    <t>precision_weighted</t>
+  </si>
+  <si>
+    <t>sensitivity_recall_weighted</t>
+  </si>
+  <si>
+    <t>specificity_macro</t>
+  </si>
+  <si>
+    <t>f1_weighted</t>
+  </si>
+  <si>
+    <t>auc_ovr_weighted</t>
+  </si>
+  <si>
+    <t>ANN</t>
+  </si>
+  <si>
+    <t>Decision Tree</t>
+  </si>
+  <si>
+    <t>K-NN</t>
+  </si>
+  <si>
+    <t>SVM</t>
+  </si>
+  <si>
+    <t>train</t>
+  </si>
+  <si>
+    <t>validation</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +95,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,417 +389,349 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>split</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>accuracy</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>precision_weighted</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>sensitivity_recall_weighted</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>specificity_macro</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>f1_weighted</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>auc_ovr_weighted</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.9686328105468425</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9685293221817567</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.9686328105468425</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.9798280278222845</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.968427932918792</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.9928389881302613</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>validation</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.9642982149107455</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9642057697100578</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9642982149107455</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9768902907221636</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.964023713019734</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.9907678308321465</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ANN</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.9699530046995301</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.969864496493862</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9699530046995301</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9805563546239338</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9697464795300955</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9924789254821275</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Decision Tree</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2">
+        <v>0.9695161586026434</v>
+      </c>
+      <c r="D2">
+        <v>0.9694228516340443</v>
+      </c>
+      <c r="E2">
+        <v>0.9695161586026434</v>
+      </c>
+      <c r="F2">
+        <v>0.9803040936603041</v>
+      </c>
+      <c r="G2">
+        <v>0.9693124775532321</v>
+      </c>
+      <c r="H2">
+        <v>0.9932590286855949</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>0.9663483174158708</v>
+      </c>
+      <c r="D3">
+        <v>0.9662880920897079</v>
+      </c>
+      <c r="E3">
+        <v>0.9663483174158708</v>
+      </c>
+      <c r="F3">
+        <v>0.9780477710212571</v>
+      </c>
+      <c r="G3">
+        <v>0.9660757861987439</v>
+      </c>
+      <c r="H3">
+        <v>0.9907239499532305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4">
+        <v>0.9695530446955305</v>
+      </c>
+      <c r="D4">
+        <v>0.9694749789664208</v>
+      </c>
+      <c r="E4">
+        <v>0.9695530446955305</v>
+      </c>
+      <c r="F4">
+        <v>0.9801448864976215</v>
+      </c>
+      <c r="G4">
+        <v>0.9693229675348857</v>
+      </c>
+      <c r="H4">
+        <v>0.9925023532980507</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="E5" t="n">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="E5">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="G5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Decision Tree</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>validation</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
         <v>0.9210960548027401</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.9209601993065444</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.9210960548027401</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.9503503886603584</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.9210057055929792</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>0.9255255829905378</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Decision Tree</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
         <v>0.9215578442155784</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>0.9215707056614443</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.9215578442155784</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.950929980133783</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>0.9215434069502429</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0.9263949702006744</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>K-NN</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
         <v>0.937282288038134</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>0.9382426734615221</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.937282288038134</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0.9573418549568928</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>0.9367091114849593</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>0.9893474404393636</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>K-NN</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>validation</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
         <v>0.9224461223061153</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>0.9236741757414144</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.9224461223061153</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.9473719405092819</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>0.9218125115615665</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>0.9619007051067705</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>K-NN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
         <v>0.9277572242775722</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>0.9289323960925385</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.9277572242775722</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>0.950797950169247</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>0.9272344324563389</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>0.9661538195465608</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>train</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11">
         <v>0.9525158752645877</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>0.9523531950337825</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.9525158752645877</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>0.967949318787508</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>0.9518445399400774</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>0.9820233042175897</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>validation</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12">
         <v>0.9488474423721186</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>0.9487195954844315</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.9488474423721186</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0.9655833291570998</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>0.9480658948683208</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>0.979140769120023</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13">
         <v>0.9547045295470453</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>0.954654060168205</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.9547045295470453</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0.9693121484525511</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>0.9541081708018527</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>0.9820562537105441</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>